--- a/rules/8.28-V7.4规则更新.xlsx
+++ b/rules/8.28-V7.4规则更新.xlsx
@@ -2647,40 +2647,154 @@
       </c>
     </row>
     <row r="27" ht="40" customHeight="1" s="12">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="11" t="n"/>
-      <c r="I27" s="11" t="n"/>
-      <c r="J27" s="11" t="n"/>
+      <c r="A27" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>管件</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>读取表格第一行“产品名称”有缝弯头90°</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>读取文本“证书编号:”20260625292</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>读取第一行“材质”Q245R GB713</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>读取“规格型号”DN1000×12 R=1.5D</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>读取页面文本厂家名，河北恒通管件集团有限公司（表格内“山东钢铁”是材料来源非制造商）</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>读取“数量”3</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>V7.6新增</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="40" customHeight="1" s="12">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="11" t="n"/>
-      <c r="I28" s="11" t="n"/>
-      <c r="J28" s="11" t="n"/>
+      <c r="A28" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>阀门</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>读取“阀门型号”逗号前段（闸阀/截止阀），多行清单每行一条</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>读取文本“编号 No:”261394-PC03</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>读取“壳体Shell”WCB</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>读取“阀门型号”逗号后段 Z41H-25 DN200（去冗余PN25）</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>读取页面文本厂家名，上海美科阀门有限公司</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>台</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>读取“数量Qty”17/9/2/2/1/2</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>V7.6新增</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="40" customHeight="1" s="12">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="11" t="n"/>
+      <c r="A29" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>法兰</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>读取“名称/描述”对焊法兰</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>读取编号 26-02-786</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>读取“材料名称”A105</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>读取“规格”WN20-600LB/RF SCH80</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>读取质保书厂家名，常州市常武欣摄石化配件有限公司</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>片</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>读取“数量”2</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>V7.6新增</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="40" customHeight="1" s="12">
       <c r="A30" s="11" t="n"/>

--- a/rules/8.28-V7.4规则更新.xlsx
+++ b/rules/8.28-V7.4规则更新.xlsx
@@ -2697,54 +2697,16 @@
       </c>
     </row>
     <row r="28" ht="40" customHeight="1" s="12">
-      <c r="A28" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>阀门</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>读取“阀门型号”逗号前段（闸阀/截止阀），多行清单每行一条</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>读取文本“编号 No:”261394-PC03</t>
-        </is>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>读取“壳体Shell”WCB</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>读取“阀门型号”逗号后段 Z41H-25 DN200（去冗余PN25）</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>读取页面文本厂家名，上海美科阀门有限公司</t>
-        </is>
-      </c>
-      <c r="H28" s="11" t="inlineStr">
-        <is>
-          <t>台</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>读取“数量Qty”17/9/2/2/1/2</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>V7.6新增</t>
-        </is>
-      </c>
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="11" t="n"/>
     </row>
     <row r="29" ht="40" customHeight="1" s="12">
       <c r="A29" s="11" t="n">
@@ -2797,16 +2759,54 @@
       </c>
     </row>
     <row r="30" ht="40" customHeight="1" s="12">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="11" t="n"/>
-      <c r="I30" s="11" t="n"/>
-      <c r="J30" s="11" t="n"/>
+      <c r="A30" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>管件</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>读取表格第一行「产品名称」</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>读取文本「证书编号:」20260815106</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>读取第一行「材质」</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>读取「规格型号」如 DN150×DN80×7/5.5</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>河北恒通管件集团有限公司（表格内「天津钢管」等是材料来源非制造商）</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>读取「数量」</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>V7.7新增</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="40" customHeight="1" s="12">
       <c r="A31" s="11" t="n"/>

--- a/rules/8.28-V7.4规则更新.xlsx
+++ b/rules/8.28-V7.4规则更新.xlsx
@@ -1327,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="5" min="1" max="1"/>
@@ -2820,6 +2820,156 @@
       <c r="I31" s="11" t="n"/>
       <c r="J31" s="11" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>法兰</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>读取“名称”承插焊法兰（产品描述表：表头含名称/规格/牌号/数量；原材料为跨行合并单元格，炉号在同列下一行）</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>读取“证明书Certificate No.”HET2024-4945</t>
+        </is>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>读取“牌号Steel Grade”A105</t>
+        </is>
+      </c>
+      <c r="F32" s="0" t="inlineStr">
+        <is>
+          <t>读取“规格Spec.”CL150 DN15 SCH80 RF</t>
+        </is>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>读取质保书最上面的厂家名，无锡市华尔泰机械制造有限公司</t>
+        </is>
+      </c>
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t>读取“数量”18</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>V7.8新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>法兰</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>读取“名称”法兰/法兰盖（产品清单多行表：表头含序号/名称/标准/规格/数量，10行去重后9条唯一）</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>（锻件产品合格证无证书编号，可手工补）</t>
+        </is>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>读取“锻件材料”S31603（表级，整批相同）</t>
+        </is>
+      </c>
+      <c r="F33" s="0" t="inlineStr">
+        <is>
+          <t>读取“规格”WN25-150 RF Sch40S 等各行列值</t>
+        </is>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>读取质保书厂家名，浙江大齐机械有限公司</t>
+        </is>
+      </c>
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>片</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="inlineStr">
+        <is>
+          <t>读取各“数量”列值</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t>V7.8新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>管材/型钢-板材</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>开会后第3份材料（12页混合质保书，11份证书拆分20条记录，测试断言编号32-51）：恒隆无缝钢管3份(去重key加规格后不再互吞)、东群钢管、石油裂化用无缝钢管(产品名称匹配放宽为任意XX钢管)、金洲镀锌管6规格逐行、唐山正丰槽钢3+角钢4(双表块按炉批号合并)、宝旭热轧卷板、武钢热轧钢带；新增分类[型钢/板材]；含甲方标签页面不继承上一页厂家</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>页内编号：质保书号/证明书号模式新增</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>各页分别提取</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>各页分别提取</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>新增映射：唐山正丰/金洲管道/武汉钢铁</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>吨/件</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>各页分别提取</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>V7.8序号32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
